--- a/assets/users_template_ar_v2.xlsx
+++ b/assets/users_template_ar_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\github\taftiche\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67068C13-FF96-4EF3-A83F-E6DFD449A278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{961B9B6F-4D40-4DE2-A1BD-0CB0954B5D0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t>المقاطعة</t>
   </si>
@@ -68,9 +68,6 @@
     <t>البريد_الإلكتروني</t>
   </si>
   <si>
-    <t>العنوان</t>
-  </si>
-  <si>
     <t>تاريخ_التعيين_بالمدرسة</t>
   </si>
   <si>
@@ -125,45 +122,18 @@
     <t>سنة_أخر_شهادة_جامعية</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>2025/2026</t>
   </si>
   <si>
-    <t>مدرسة الرافدين الأولى</t>
-  </si>
-  <si>
     <t>أنثى</t>
   </si>
   <si>
-    <t>علمي</t>
-  </si>
-  <si>
     <t>متزوج</t>
   </si>
   <si>
-    <t>02-10-2006</t>
-  </si>
-  <si>
     <t>مترسمة</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>21-10-2010</t>
-  </si>
-  <si>
-    <t>10-02-2026</t>
-  </si>
-  <si>
-    <t>11-11-2025</t>
-  </si>
-  <si>
-    <t>الرابعة</t>
-  </si>
-  <si>
     <t>تنسيق التواريخ المطلوب: DD-MM-YYYY (مثال: 16-01-1976)</t>
   </si>
   <si>
@@ -176,32 +146,50 @@
     <t>يمكن ترك الحقول الاختيارية فارغة إذا لم تكن مطلوبة.</t>
   </si>
   <si>
-    <t>فريال</t>
-  </si>
-  <si>
-    <t>آريس</t>
-  </si>
-  <si>
-    <t>ferial@afichte.com</t>
-  </si>
-  <si>
-    <t>مهندسة</t>
-  </si>
-  <si>
-    <t>البخاري بسكرة</t>
-  </si>
-  <si>
-    <t>0652223344</t>
-  </si>
-  <si>
-    <t>أستاذ تعليم إبتدائي مميز</t>
+    <t>جنايحي الهادي بن الصادق</t>
+  </si>
+  <si>
+    <t>حي 400 مسكن عدل بسكرة</t>
+  </si>
+  <si>
+    <t>صوالي</t>
+  </si>
+  <si>
+    <t>لامية</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تشير</t>
+  </si>
+  <si>
+    <t>سطيف</t>
+  </si>
+  <si>
+    <t>ليسانس أدب عربي</t>
+  </si>
+  <si>
+    <t>أستاذ تعليم إبتدائي قسم أول</t>
+  </si>
+  <si>
+    <t>الخامسة</t>
+  </si>
+  <si>
+    <t>الأولى</t>
+  </si>
+  <si>
+    <t>نعم</t>
+  </si>
+  <si>
+    <t>0668242061</t>
+  </si>
+  <si>
+    <t>sawali@gmail.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -212,23 +200,23 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -240,24 +228,54 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="4" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -268,6 +286,48 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{9836F353-D43D-4848-BF37-D583978B88E3}" name="Tableau5" displayName="Tableau5" ref="A1:AG50" totalsRowShown="0" headerRowDxfId="0">
+  <autoFilter ref="A1:AG50" xr:uid="{9836F353-D43D-4848-BF37-D583978B88E3}"/>
+  <tableColumns count="33">
+    <tableColumn id="1" xr3:uid="{2191AF52-6F73-4282-BEBE-F23021EB92DA}" name="المقاطعة"/>
+    <tableColumn id="2" xr3:uid="{B3D4CF38-F863-4A28-8492-E4337038C97E}" name="العام الدراسي"/>
+    <tableColumn id="3" xr3:uid="{EEC76A0F-0680-4430-9B39-AD2EEDF9F139}" name="اسم_المؤسسة"/>
+    <tableColumn id="4" xr3:uid="{F4EBB4C4-59B2-405B-B587-C3C5FED1CC4C}" name="سنوات_العمل"/>
+    <tableColumn id="5" xr3:uid="{A8089D34-0600-4584-9F05-8597F1B25DFE}" name="الجنس"/>
+    <tableColumn id="6" xr3:uid="{F87B8EB9-BF3A-49ED-A292-95281618D535}" name="الاسم_الشخصي"/>
+    <tableColumn id="7" xr3:uid="{C90EBE41-B6AE-4EB8-A856-4A1BD564ADC3}" name="الاسم_العائلي"/>
+    <tableColumn id="8" xr3:uid="{87E350D1-B2E2-43FD-8B06-6F3A1A30A6B1}" name="الاسم_الأصلي_للمتزوجة"/>
+    <tableColumn id="9" xr3:uid="{2F3BE7D8-0E23-4EE4-A1A6-31C390C76820}" name="تاريخ_الازدياد"/>
+    <tableColumn id="10" xr3:uid="{3D14CF71-32FC-46A4-96B4-C7AAE990BAB3}" name="مكان_الازدياد"/>
+    <tableColumn id="11" xr3:uid="{87D0D0DC-41DE-4F24-B347-AFC245C8FDCB}" name="الإقامة"/>
+    <tableColumn id="12" xr3:uid="{75CB7CE5-CDBD-4344-ACB2-FCC52F3373CF}" name="الوضعية_العائلية"/>
+    <tableColumn id="13" xr3:uid="{0A0293AB-30C2-49E3-BB49-2F725B577567}" name="عدد_الأبناء"/>
+    <tableColumn id="14" xr3:uid="{9F042F4E-5D98-4ABD-839A-64B4AC718657}" name="رقم_الهاتف"/>
+    <tableColumn id="15" xr3:uid="{9F088BFC-CFF5-44C0-B856-4D0970B6B6DA}" name="البريد_الإلكتروني"/>
+    <tableColumn id="16" xr3:uid="{DA413614-77BF-430A-B396-2AD3B8344C33}" name="تاريخ_التعيين_بالمدرسة"/>
+    <tableColumn id="17" xr3:uid="{7E09C74F-4455-4FAE-A345-A7B1DC982974}" name="الشهادة"/>
+    <tableColumn id="18" xr3:uid="{CF7C12A4-2C11-4A12-BC0D-0910E3927AD3}" name="تاريخ_التعيين_الأول"/>
+    <tableColumn id="19" xr3:uid="{22E13157-C359-4F2D-A590-059E54F94D5A}" name="الرتبة"/>
+    <tableColumn id="20" xr3:uid="{2E98A8CA-B7AC-42BD-94BD-41114C46F4DA}" name="الوضعية_الإدارية"/>
+    <tableColumn id="21" xr3:uid="{DF7F57E7-73E5-411F-AE65-627ED1AA6284}" name="السلم"/>
+    <tableColumn id="22" xr3:uid="{59B8E39E-3DAF-4F1C-B083-BE818608B2BD}" name="الدرجة"/>
+    <tableColumn id="23" xr3:uid="{39617AB7-378F-42B8-9F36-2BDD4DEAFE8D}" name="تاريخ_السريان"/>
+    <tableColumn id="24" xr3:uid="{413C9FD0-C0C2-41E5-8D88-FD0AA15CBC09}" name="تاريخ_التفتيش_قبل_الأخير"/>
+    <tableColumn id="25" xr3:uid="{5637426C-4D46-41B5-8B7E-1C3970F1E1D4}" name="علامة_التفتيش_قبل_الأخير"/>
+    <tableColumn id="26" xr3:uid="{CD058622-5E21-4289-9C92-4E010BC2E06F}" name="تاريخ_آخر_تفتيش"/>
+    <tableColumn id="27" xr3:uid="{EDFF467E-5747-4BD7-B9C2-37F8CAAB3A8D}" name="علامة_آخر_تفتيش"/>
+    <tableColumn id="28" xr3:uid="{5C544824-A2D5-4335-BC9A-23F6BA35A17C}" name="فصل_السنة_الماضية"/>
+    <tableColumn id="29" xr3:uid="{8901F83F-02A9-42C9-9F9C-9D144FDA1EA0}" name="عدد_التلاميذ"/>
+    <tableColumn id="30" xr3:uid="{EC29551F-65DA-433F-A37C-9D4B542FD081}" name="فصل_السنة_الحالية"/>
+    <tableColumn id="31" xr3:uid="{1E37DCF4-054D-4740-8CCF-1987BFDF5D75}" name="حركة"/>
+    <tableColumn id="32" xr3:uid="{974E0314-7992-465C-8AA3-4A772F1E81FC}" name="سنة_تخرج_المعهد_التقني"/>
+    <tableColumn id="33" xr3:uid="{E6CE4F24-CE8E-4E27-810E-6F5A77A937C9}" name="سنة_أخر_شهادة_جامعية"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -555,13 +615,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AG50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="34" width="22" customWidth="1"/>
+    <col min="1" max="33" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -661,116 +721,1789 @@
       <c r="AG1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" spans="1:34" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>11</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="C2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D2" s="2">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I2" s="3">
+        <v>29631</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C3" t="s">
+      <c r="M2" s="2">
+        <v>4</v>
+      </c>
+      <c r="N2" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2" s="3">
+        <v>41175</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="T2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D3">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="U2" s="2">
+        <v>13</v>
+      </c>
+      <c r="V2" s="2">
+        <v>5</v>
+      </c>
+      <c r="W2" s="3">
+        <v>45108</v>
+      </c>
+      <c r="X2" s="3">
+        <v>45611</v>
+      </c>
+      <c r="Y2" s="2">
+        <v>14</v>
+      </c>
+      <c r="Z2" s="3">
+        <v>46000</v>
+      </c>
+      <c r="AA2" s="2">
+        <v>15</v>
+      </c>
+      <c r="AB2" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC2" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="AE2" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G3" t="s">
-        <v>38</v>
-      </c>
-      <c r="H3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I3" s="2">
-        <v>28204</v>
-      </c>
-      <c r="J3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K3" t="s">
-        <v>52</v>
-      </c>
-      <c r="L3" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3">
-        <v>5</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="P3" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>40</v>
-      </c>
-      <c r="R3" t="s">
-        <v>54</v>
-      </c>
-      <c r="S3" s="2">
-        <v>42767</v>
-      </c>
-      <c r="T3" t="s">
-        <v>57</v>
-      </c>
-      <c r="U3" t="s">
-        <v>41</v>
-      </c>
-      <c r="V3" t="s">
-        <v>34</v>
-      </c>
-      <c r="W3" t="s">
-        <v>42</v>
-      </c>
-      <c r="X3" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y3" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z3">
-        <v>14</v>
-      </c>
-      <c r="AA3" t="s">
-        <v>45</v>
-      </c>
-      <c r="AB3">
-        <v>15</v>
-      </c>
-      <c r="AC3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AD3">
-        <v>36</v>
-      </c>
-      <c r="AE3" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AH3">
-        <v>2017</v>
-      </c>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+      <c r="AA3" s="2"/>
+      <c r="AB3" s="2"/>
+      <c r="AC3" s="2"/>
+      <c r="AD3" s="2"/>
+      <c r="AE3" s="2"/>
+      <c r="AF3" s="2"/>
+      <c r="AG3" s="2"/>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+      <c r="AA4" s="2"/>
+      <c r="AB4" s="2"/>
+      <c r="AC4" s="2"/>
+      <c r="AD4" s="2"/>
+      <c r="AE4" s="2"/>
+      <c r="AF4" s="2"/>
+      <c r="AG4" s="2"/>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+      <c r="AA5" s="2"/>
+      <c r="AB5" s="2"/>
+      <c r="AC5" s="2"/>
+      <c r="AD5" s="2"/>
+      <c r="AE5" s="2"/>
+      <c r="AF5" s="2"/>
+      <c r="AG5" s="2"/>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+      <c r="AA6" s="2"/>
+      <c r="AB6" s="2"/>
+      <c r="AC6" s="2"/>
+      <c r="AD6" s="2"/>
+      <c r="AE6" s="2"/>
+      <c r="AF6" s="2"/>
+      <c r="AG6" s="2"/>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+      <c r="AA7" s="2"/>
+      <c r="AB7" s="2"/>
+      <c r="AC7" s="2"/>
+      <c r="AD7" s="2"/>
+      <c r="AE7" s="2"/>
+      <c r="AF7" s="2"/>
+      <c r="AG7" s="2"/>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A8" s="2"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+      <c r="AA8" s="2"/>
+      <c r="AB8" s="2"/>
+      <c r="AC8" s="2"/>
+      <c r="AD8" s="2"/>
+      <c r="AE8" s="2"/>
+      <c r="AF8" s="2"/>
+      <c r="AG8" s="2"/>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+      <c r="AA9" s="2"/>
+      <c r="AB9" s="2"/>
+      <c r="AC9" s="2"/>
+      <c r="AD9" s="2"/>
+      <c r="AE9" s="2"/>
+      <c r="AF9" s="2"/>
+      <c r="AG9" s="2"/>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A10" s="2"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+      <c r="AA10" s="2"/>
+      <c r="AB10" s="2"/>
+      <c r="AC10" s="2"/>
+      <c r="AD10" s="2"/>
+      <c r="AE10" s="2"/>
+      <c r="AF10" s="2"/>
+      <c r="AG10" s="2"/>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
+      <c r="AA11" s="2"/>
+      <c r="AB11" s="2"/>
+      <c r="AC11" s="2"/>
+      <c r="AD11" s="2"/>
+      <c r="AE11" s="2"/>
+      <c r="AF11" s="2"/>
+      <c r="AG11" s="2"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A12" s="2"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
+      <c r="AA12" s="2"/>
+      <c r="AB12" s="2"/>
+      <c r="AC12" s="2"/>
+      <c r="AD12" s="2"/>
+      <c r="AE12" s="2"/>
+      <c r="AF12" s="2"/>
+      <c r="AG12" s="2"/>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
+      <c r="Z13" s="2"/>
+      <c r="AA13" s="2"/>
+      <c r="AB13" s="2"/>
+      <c r="AC13" s="2"/>
+      <c r="AD13" s="2"/>
+      <c r="AE13" s="2"/>
+      <c r="AF13" s="2"/>
+      <c r="AG13" s="2"/>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
+      <c r="Z14" s="2"/>
+      <c r="AA14" s="2"/>
+      <c r="AB14" s="2"/>
+      <c r="AC14" s="2"/>
+      <c r="AD14" s="2"/>
+      <c r="AE14" s="2"/>
+      <c r="AF14" s="2"/>
+      <c r="AG14" s="2"/>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A15" s="2"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+      <c r="AA15" s="2"/>
+      <c r="AB15" s="2"/>
+      <c r="AC15" s="2"/>
+      <c r="AD15" s="2"/>
+      <c r="AE15" s="2"/>
+      <c r="AF15" s="2"/>
+      <c r="AG15" s="2"/>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A16" s="2"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
+      <c r="AA16" s="2"/>
+      <c r="AB16" s="2"/>
+      <c r="AC16" s="2"/>
+      <c r="AD16" s="2"/>
+      <c r="AE16" s="2"/>
+      <c r="AF16" s="2"/>
+      <c r="AG16" s="2"/>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A17" s="2"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
+      <c r="AA17" s="2"/>
+      <c r="AB17" s="2"/>
+      <c r="AC17" s="2"/>
+      <c r="AD17" s="2"/>
+      <c r="AE17" s="2"/>
+      <c r="AF17" s="2"/>
+      <c r="AG17" s="2"/>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A18" s="2"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+      <c r="AA18" s="2"/>
+      <c r="AB18" s="2"/>
+      <c r="AC18" s="2"/>
+      <c r="AD18" s="2"/>
+      <c r="AE18" s="2"/>
+      <c r="AF18" s="2"/>
+      <c r="AG18" s="2"/>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+      <c r="AA19" s="2"/>
+      <c r="AB19" s="2"/>
+      <c r="AC19" s="2"/>
+      <c r="AD19" s="2"/>
+      <c r="AE19" s="2"/>
+      <c r="AF19" s="2"/>
+      <c r="AG19" s="2"/>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+      <c r="AA20" s="2"/>
+      <c r="AB20" s="2"/>
+      <c r="AC20" s="2"/>
+      <c r="AD20" s="2"/>
+      <c r="AE20" s="2"/>
+      <c r="AF20" s="2"/>
+      <c r="AG20" s="2"/>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A21" s="2"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
+      <c r="AA21" s="2"/>
+      <c r="AB21" s="2"/>
+      <c r="AC21" s="2"/>
+      <c r="AD21" s="2"/>
+      <c r="AE21" s="2"/>
+      <c r="AF21" s="2"/>
+      <c r="AG21" s="2"/>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A22" s="2"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="2"/>
+      <c r="Z22" s="2"/>
+      <c r="AA22" s="2"/>
+      <c r="AB22" s="2"/>
+      <c r="AC22" s="2"/>
+      <c r="AD22" s="2"/>
+      <c r="AE22" s="2"/>
+      <c r="AF22" s="2"/>
+      <c r="AG22" s="2"/>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="2"/>
+      <c r="Z23" s="2"/>
+      <c r="AA23" s="2"/>
+      <c r="AB23" s="2"/>
+      <c r="AC23" s="2"/>
+      <c r="AD23" s="2"/>
+      <c r="AE23" s="2"/>
+      <c r="AF23" s="2"/>
+      <c r="AG23" s="2"/>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A24" s="2"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2"/>
+      <c r="Z24" s="2"/>
+      <c r="AA24" s="2"/>
+      <c r="AB24" s="2"/>
+      <c r="AC24" s="2"/>
+      <c r="AD24" s="2"/>
+      <c r="AE24" s="2"/>
+      <c r="AF24" s="2"/>
+      <c r="AG24" s="2"/>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="2"/>
+      <c r="Z25" s="2"/>
+      <c r="AA25" s="2"/>
+      <c r="AB25" s="2"/>
+      <c r="AC25" s="2"/>
+      <c r="AD25" s="2"/>
+      <c r="AE25" s="2"/>
+      <c r="AF25" s="2"/>
+      <c r="AG25" s="2"/>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
+      <c r="Z26" s="2"/>
+      <c r="AA26" s="2"/>
+      <c r="AB26" s="2"/>
+      <c r="AC26" s="2"/>
+      <c r="AD26" s="2"/>
+      <c r="AE26" s="2"/>
+      <c r="AF26" s="2"/>
+      <c r="AG26" s="2"/>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A27" s="2"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="2"/>
+      <c r="Z27" s="2"/>
+      <c r="AA27" s="2"/>
+      <c r="AB27" s="2"/>
+      <c r="AC27" s="2"/>
+      <c r="AD27" s="2"/>
+      <c r="AE27" s="2"/>
+      <c r="AF27" s="2"/>
+      <c r="AG27" s="2"/>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+      <c r="V28" s="2"/>
+      <c r="W28" s="2"/>
+      <c r="X28" s="2"/>
+      <c r="Y28" s="2"/>
+      <c r="Z28" s="2"/>
+      <c r="AA28" s="2"/>
+      <c r="AB28" s="2"/>
+      <c r="AC28" s="2"/>
+      <c r="AD28" s="2"/>
+      <c r="AE28" s="2"/>
+      <c r="AF28" s="2"/>
+      <c r="AG28" s="2"/>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A29" s="2"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+      <c r="V29" s="2"/>
+      <c r="W29" s="2"/>
+      <c r="X29" s="2"/>
+      <c r="Y29" s="2"/>
+      <c r="Z29" s="2"/>
+      <c r="AA29" s="2"/>
+      <c r="AB29" s="2"/>
+      <c r="AC29" s="2"/>
+      <c r="AD29" s="2"/>
+      <c r="AE29" s="2"/>
+      <c r="AF29" s="2"/>
+      <c r="AG29" s="2"/>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A30" s="2"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="2"/>
+      <c r="Z30" s="2"/>
+      <c r="AA30" s="2"/>
+      <c r="AB30" s="2"/>
+      <c r="AC30" s="2"/>
+      <c r="AD30" s="2"/>
+      <c r="AE30" s="2"/>
+      <c r="AF30" s="2"/>
+      <c r="AG30" s="2"/>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A31" s="2"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="2"/>
+      <c r="R31" s="2"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="2"/>
+      <c r="U31" s="2"/>
+      <c r="V31" s="2"/>
+      <c r="W31" s="2"/>
+      <c r="X31" s="2"/>
+      <c r="Y31" s="2"/>
+      <c r="Z31" s="2"/>
+      <c r="AA31" s="2"/>
+      <c r="AB31" s="2"/>
+      <c r="AC31" s="2"/>
+      <c r="AD31" s="2"/>
+      <c r="AE31" s="2"/>
+      <c r="AF31" s="2"/>
+      <c r="AG31" s="2"/>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A32" s="2"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="2"/>
+      <c r="X32" s="2"/>
+      <c r="Y32" s="2"/>
+      <c r="Z32" s="2"/>
+      <c r="AA32" s="2"/>
+      <c r="AB32" s="2"/>
+      <c r="AC32" s="2"/>
+      <c r="AD32" s="2"/>
+      <c r="AE32" s="2"/>
+      <c r="AF32" s="2"/>
+      <c r="AG32" s="2"/>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A33" s="2"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="2"/>
+      <c r="X33" s="2"/>
+      <c r="Y33" s="2"/>
+      <c r="Z33" s="2"/>
+      <c r="AA33" s="2"/>
+      <c r="AB33" s="2"/>
+      <c r="AC33" s="2"/>
+      <c r="AD33" s="2"/>
+      <c r="AE33" s="2"/>
+      <c r="AF33" s="2"/>
+      <c r="AG33" s="2"/>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A34" s="2"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="2"/>
+      <c r="X34" s="2"/>
+      <c r="Y34" s="2"/>
+      <c r="Z34" s="2"/>
+      <c r="AA34" s="2"/>
+      <c r="AB34" s="2"/>
+      <c r="AC34" s="2"/>
+      <c r="AD34" s="2"/>
+      <c r="AE34" s="2"/>
+      <c r="AF34" s="2"/>
+      <c r="AG34" s="2"/>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A35" s="2"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
+      <c r="W35" s="2"/>
+      <c r="X35" s="2"/>
+      <c r="Y35" s="2"/>
+      <c r="Z35" s="2"/>
+      <c r="AA35" s="2"/>
+      <c r="AB35" s="2"/>
+      <c r="AC35" s="2"/>
+      <c r="AD35" s="2"/>
+      <c r="AE35" s="2"/>
+      <c r="AF35" s="2"/>
+      <c r="AG35" s="2"/>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
+      <c r="W36" s="2"/>
+      <c r="X36" s="2"/>
+      <c r="Y36" s="2"/>
+      <c r="Z36" s="2"/>
+      <c r="AA36" s="2"/>
+      <c r="AB36" s="2"/>
+      <c r="AC36" s="2"/>
+      <c r="AD36" s="2"/>
+      <c r="AE36" s="2"/>
+      <c r="AF36" s="2"/>
+      <c r="AG36" s="2"/>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A37" s="2"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
+      <c r="W37" s="2"/>
+      <c r="X37" s="2"/>
+      <c r="Y37" s="2"/>
+      <c r="Z37" s="2"/>
+      <c r="AA37" s="2"/>
+      <c r="AB37" s="2"/>
+      <c r="AC37" s="2"/>
+      <c r="AD37" s="2"/>
+      <c r="AE37" s="2"/>
+      <c r="AF37" s="2"/>
+      <c r="AG37" s="2"/>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="R38" s="2"/>
+      <c r="S38" s="2"/>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="2"/>
+      <c r="X38" s="2"/>
+      <c r="Y38" s="2"/>
+      <c r="Z38" s="2"/>
+      <c r="AA38" s="2"/>
+      <c r="AB38" s="2"/>
+      <c r="AC38" s="2"/>
+      <c r="AD38" s="2"/>
+      <c r="AE38" s="2"/>
+      <c r="AF38" s="2"/>
+      <c r="AG38" s="2"/>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A39" s="2"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
+      <c r="G39" s="2"/>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="2"/>
+      <c r="R39" s="2"/>
+      <c r="S39" s="2"/>
+      <c r="T39" s="2"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="2"/>
+      <c r="W39" s="2"/>
+      <c r="X39" s="2"/>
+      <c r="Y39" s="2"/>
+      <c r="Z39" s="2"/>
+      <c r="AA39" s="2"/>
+      <c r="AB39" s="2"/>
+      <c r="AC39" s="2"/>
+      <c r="AD39" s="2"/>
+      <c r="AE39" s="2"/>
+      <c r="AF39" s="2"/>
+      <c r="AG39" s="2"/>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2"/>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="R40" s="2"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="2"/>
+      <c r="U40" s="2"/>
+      <c r="V40" s="2"/>
+      <c r="W40" s="2"/>
+      <c r="X40" s="2"/>
+      <c r="Y40" s="2"/>
+      <c r="Z40" s="2"/>
+      <c r="AA40" s="2"/>
+      <c r="AB40" s="2"/>
+      <c r="AC40" s="2"/>
+      <c r="AD40" s="2"/>
+      <c r="AE40" s="2"/>
+      <c r="AF40" s="2"/>
+      <c r="AG40" s="2"/>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
+      <c r="F41" s="2"/>
+      <c r="G41" s="2"/>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="2"/>
+      <c r="R41" s="2"/>
+      <c r="S41" s="2"/>
+      <c r="T41" s="2"/>
+      <c r="U41" s="2"/>
+      <c r="V41" s="2"/>
+      <c r="W41" s="2"/>
+      <c r="X41" s="2"/>
+      <c r="Y41" s="2"/>
+      <c r="Z41" s="2"/>
+      <c r="AA41" s="2"/>
+      <c r="AB41" s="2"/>
+      <c r="AC41" s="2"/>
+      <c r="AD41" s="2"/>
+      <c r="AE41" s="2"/>
+      <c r="AF41" s="2"/>
+      <c r="AG41" s="2"/>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A42" s="2"/>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
+      <c r="D42" s="2"/>
+      <c r="E42" s="2"/>
+      <c r="F42" s="2"/>
+      <c r="G42" s="2"/>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="2"/>
+      <c r="R42" s="2"/>
+      <c r="S42" s="2"/>
+      <c r="T42" s="2"/>
+      <c r="U42" s="2"/>
+      <c r="V42" s="2"/>
+      <c r="W42" s="2"/>
+      <c r="X42" s="2"/>
+      <c r="Y42" s="2"/>
+      <c r="Z42" s="2"/>
+      <c r="AA42" s="2"/>
+      <c r="AB42" s="2"/>
+      <c r="AC42" s="2"/>
+      <c r="AD42" s="2"/>
+      <c r="AE42" s="2"/>
+      <c r="AF42" s="2"/>
+      <c r="AG42" s="2"/>
+    </row>
+    <row r="43" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A43" s="2"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+      <c r="D43" s="2"/>
+      <c r="E43" s="2"/>
+      <c r="F43" s="2"/>
+      <c r="G43" s="2"/>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="2"/>
+      <c r="T43" s="2"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="2"/>
+      <c r="W43" s="2"/>
+      <c r="X43" s="2"/>
+      <c r="Y43" s="2"/>
+      <c r="Z43" s="2"/>
+      <c r="AA43" s="2"/>
+      <c r="AB43" s="2"/>
+      <c r="AC43" s="2"/>
+      <c r="AD43" s="2"/>
+      <c r="AE43" s="2"/>
+      <c r="AF43" s="2"/>
+      <c r="AG43" s="2"/>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A44" s="2"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+      <c r="D44" s="2"/>
+      <c r="E44" s="2"/>
+      <c r="F44" s="2"/>
+      <c r="G44" s="2"/>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="2"/>
+      <c r="R44" s="2"/>
+      <c r="S44" s="2"/>
+      <c r="T44" s="2"/>
+      <c r="U44" s="2"/>
+      <c r="V44" s="2"/>
+      <c r="W44" s="2"/>
+      <c r="X44" s="2"/>
+      <c r="Y44" s="2"/>
+      <c r="Z44" s="2"/>
+      <c r="AA44" s="2"/>
+      <c r="AB44" s="2"/>
+      <c r="AC44" s="2"/>
+      <c r="AD44" s="2"/>
+      <c r="AE44" s="2"/>
+      <c r="AF44" s="2"/>
+      <c r="AG44" s="2"/>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+      <c r="D45" s="2"/>
+      <c r="E45" s="2"/>
+      <c r="F45" s="2"/>
+      <c r="G45" s="2"/>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="2"/>
+      <c r="R45" s="2"/>
+      <c r="S45" s="2"/>
+      <c r="T45" s="2"/>
+      <c r="U45" s="2"/>
+      <c r="V45" s="2"/>
+      <c r="W45" s="2"/>
+      <c r="X45" s="2"/>
+      <c r="Y45" s="2"/>
+      <c r="Z45" s="2"/>
+      <c r="AA45" s="2"/>
+      <c r="AB45" s="2"/>
+      <c r="AC45" s="2"/>
+      <c r="AD45" s="2"/>
+      <c r="AE45" s="2"/>
+      <c r="AF45" s="2"/>
+      <c r="AG45" s="2"/>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A46" s="2"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="2"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="G46" s="2"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2"/>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="2"/>
+      <c r="R46" s="2"/>
+      <c r="S46" s="2"/>
+      <c r="T46" s="2"/>
+      <c r="U46" s="2"/>
+      <c r="V46" s="2"/>
+      <c r="W46" s="2"/>
+      <c r="X46" s="2"/>
+      <c r="Y46" s="2"/>
+      <c r="Z46" s="2"/>
+      <c r="AA46" s="2"/>
+      <c r="AB46" s="2"/>
+      <c r="AC46" s="2"/>
+      <c r="AD46" s="2"/>
+      <c r="AE46" s="2"/>
+      <c r="AF46" s="2"/>
+      <c r="AG46" s="2"/>
+    </row>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="2"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="2"/>
+      <c r="R47" s="2"/>
+      <c r="S47" s="2"/>
+      <c r="T47" s="2"/>
+      <c r="U47" s="2"/>
+      <c r="V47" s="2"/>
+      <c r="W47" s="2"/>
+      <c r="X47" s="2"/>
+      <c r="Y47" s="2"/>
+      <c r="Z47" s="2"/>
+      <c r="AA47" s="2"/>
+      <c r="AB47" s="2"/>
+      <c r="AC47" s="2"/>
+      <c r="AD47" s="2"/>
+      <c r="AE47" s="2"/>
+      <c r="AF47" s="2"/>
+      <c r="AG47" s="2"/>
+    </row>
+    <row r="48" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A48" s="2"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="2"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="2"/>
+      <c r="G48" s="2"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="2"/>
+      <c r="R48" s="2"/>
+      <c r="S48" s="2"/>
+      <c r="T48" s="2"/>
+      <c r="U48" s="2"/>
+      <c r="V48" s="2"/>
+      <c r="W48" s="2"/>
+      <c r="X48" s="2"/>
+      <c r="Y48" s="2"/>
+      <c r="Z48" s="2"/>
+      <c r="AA48" s="2"/>
+      <c r="AB48" s="2"/>
+      <c r="AC48" s="2"/>
+      <c r="AD48" s="2"/>
+      <c r="AE48" s="2"/>
+      <c r="AF48" s="2"/>
+      <c r="AG48" s="2"/>
+    </row>
+    <row r="49" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A49" s="2"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="2"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="2"/>
+      <c r="R49" s="2"/>
+      <c r="S49" s="2"/>
+      <c r="T49" s="2"/>
+      <c r="U49" s="2"/>
+      <c r="V49" s="2"/>
+      <c r="W49" s="2"/>
+      <c r="X49" s="2"/>
+      <c r="Y49" s="2"/>
+      <c r="Z49" s="2"/>
+      <c r="AA49" s="2"/>
+      <c r="AB49" s="2"/>
+      <c r="AC49" s="2"/>
+      <c r="AD49" s="2"/>
+      <c r="AE49" s="2"/>
+      <c r="AF49" s="2"/>
+      <c r="AG49" s="2"/>
+    </row>
+    <row r="50" spans="1:33" x14ac:dyDescent="0.35">
+      <c r="A50" s="2"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+      <c r="D50" s="2"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2"/>
+      <c r="Q50" s="2"/>
+      <c r="R50" s="2"/>
+      <c r="S50" s="2"/>
+      <c r="T50" s="2"/>
+      <c r="U50" s="2"/>
+      <c r="V50" s="2"/>
+      <c r="W50" s="2"/>
+      <c r="X50" s="2"/>
+      <c r="Y50" s="2"/>
+      <c r="Z50" s="2"/>
+      <c r="AA50" s="2"/>
+      <c r="AB50" s="2"/>
+      <c r="AC50" s="2"/>
+      <c r="AD50" s="2"/>
+      <c r="AE50" s="2"/>
+      <c r="AF50" s="2"/>
+      <c r="AG50" s="2"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="O3" r:id="rId1" xr:uid="{89B0BC0A-A97D-4F36-9BAB-2593835CD8D0}"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -781,22 +2514,22 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
